--- a/output/ValueSet-vs-tissue-glucose-cgm.xlsx
+++ b/output/ValueSet-vs-tissue-glucose-cgm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-19T17:49:48+02:00</t>
+    <t>2025-08-20T09:32:40+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/ValueSet-vs-tissue-glucose-cgm.xlsx
+++ b/output/ValueSet-vs-tissue-glucose-cgm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-20T09:32:40+02:00</t>
+    <t>2025-08-21T10:18:14+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/ValueSet-vs-tissue-glucose-cgm.xlsx
+++ b/output/ValueSet-vs-tissue-glucose-cgm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-21T10:18:14+02:00</t>
+    <t>2025-08-21T11:34:25+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/ValueSet-vs-tissue-glucose-cgm.xlsx
+++ b/output/ValueSet-vs-tissue-glucose-cgm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-21T11:34:25+02:00</t>
+    <t>2025-08-21T15:49:15+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
